--- a/reports/集团总公司_利润表_2025-09.xlsx
+++ b/reports/集团总公司_利润表_2025-09.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>229707090</v>
+        <v>250761971</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>174652632</v>
+        <v>189785711</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1518777184</v>
+        <v>1648786588</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>714551</v>
+        <v>923470</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>6196936</v>
+        <v>8014009</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>620798</v>
+        <v>809497</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>5377387</v>
+        <v>7014154</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>523298</v>
+        <v>684381</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4554172</v>
+        <v>5922638</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>482946</v>
+        <v>632405</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4190960</v>
+        <v>5468366</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>261020</v>
+        <v>347961</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2276007</v>
+        <v>3008118</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>209674</v>
+        <v>274069</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1821500</v>
+        <v>2370176</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>226894803</v>
+        <v>247090188</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>171840345</v>
+        <v>186113928</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>88577708</v>
+        <v>97359345</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>769347980</v>
+        <v>843208827</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1627739</v>
+        <v>2880062</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>14117015</v>
+        <v>25047178</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1474973</v>
+        <v>2092332</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>12757103</v>
+        <v>18212584</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>78382435</v>
+        <v>82474260</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>682895578</v>
+        <v>719075850</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1689847</v>
+        <v>2090958</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>14586091</v>
+        <v>18206081</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>734329</v>
+        <v>1047232</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>6377022</v>
+        <v>9104581</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2638821</v>
+        <v>3146364</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>22790758</v>
+        <v>27317000</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1154519</v>
+        <v>1575220</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>10022652</v>
+        <v>13661665</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>54884378</v>
+        <v>55217744</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>476448823</v>
+        <v>476824292</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>170080</v>
+        <v>170647</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1530093</v>
+        <v>1530873</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3352694</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>28985157</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2235175</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>19325630</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>165985930</v>
+        <v>188619635</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>133207322</v>
+        <v>141092999</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>104652826</v>
+        <v>112792320</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>911672932</v>
+        <v>977156495</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28554496</v>
+        <v>28300679</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>246982873</v>
+        <v>246706956</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5549183</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>48272694</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1773919</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>15443603</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1108320</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>9650732</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1330516</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>11580291</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>998957</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>8685787</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>667007</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5791508</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>556818</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4827437</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3085454</v>
+        <v>3106531</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>26865410</v>
+        <v>26880958</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1461834</v>
+        <v>1463776</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>12667034</v>
+        <v>12664883</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3768170</v>
+        <v>3794219</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>32783961</v>
+        <v>32818770</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>24459821</v>
+        <v>24529125</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>212262135</v>
+        <v>212388775</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>348537</v>
+        <v>2990941</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3147881</v>
+        <v>25970136</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1116626</v>
+        <v>1121100</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>10075642</v>
+        <v>10083229</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1161342</v>
+        <v>1070620</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>10439768</v>
+        <v>9632158</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>119617</v>
+        <v>119855</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1079499</v>
+        <v>1079969</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>475564</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>4291410</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>970027</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>8445499</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>316666</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2860012</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>237617</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2145030</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>396484</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3575525</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1389915</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>12065989</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212170</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1907930</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159386</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1431362</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>265959</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2386196</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>186275</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1670604</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>133031</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1193339</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>106331</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>954595</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79634</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>715810</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>60908873</v>
+        <v>61837713</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>65895765</v>
+        <v>65631628</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>554735</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4826939</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>131966</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1191776</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>209916</v>
+        <v>209127</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1890079</v>
+        <v>1888680</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>60698957</v>
+        <v>62183321</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7090862</v>
+        <v>7081636</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>63900804</v>
+        <v>63864246</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>53608095</v>
+        <v>55101685</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>53608095</v>
+        <v>55101685</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>53608095</v>
+        <v>55101685</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>53608095</v>
+        <v>55101685</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>53608095</v>
+        <v>55101685</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
